--- a/artfynd/A 55934-2023 artfynd.xlsx
+++ b/artfynd/A 55934-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126560146</v>
       </c>
       <c r="B2" t="n">
-        <v>96650</v>
+        <v>96725</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>126560145</v>
       </c>
       <c r="B3" t="n">
-        <v>95964</v>
+        <v>96039</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
